--- a/data/trans_orig/IP16A07-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP16A07-Habitat-trans_orig.xlsx
@@ -3028,7 +3028,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3308</t>
+          <t>3909</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3043,7 +3043,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3350</t>
+          <t>3277</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>37716</t>
+          <t>37115</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>77994</t>
+          <t>78067</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4057,7 +4057,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3282</t>
+          <t>3768</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4127,7 +4127,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3937</t>
+          <t>3038</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -4165,7 +4165,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>143939</t>
+          <t>143453</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4235,7 +4235,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>301250</t>
+          <t>302149</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -6922,7 +6922,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4616</t>
+          <t>4035</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6937,7 +6937,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6992,7 +6992,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3698</t>
+          <t>3662</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -7030,7 +7030,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>39626</t>
+          <t>40207</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>104353</t>
+          <t>104389</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -7115,7 +7115,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7265,7 +7265,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4911</t>
+          <t>5411</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7280,7 +7280,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7335,7 +7335,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4981</t>
+          <t>4902</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7350,7 +7350,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -7373,7 +7373,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>72160</t>
+          <t>71660</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>129013</t>
+          <t>129092</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -7458,7 +7458,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>545</t>
+          <t>497</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6682</t>
+          <t>5750</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>555</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5737</t>
+          <t>5688</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>171033</t>
+          <t>171965</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>177170</t>
+          <t>177218</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>354179</t>
+          <t>354228</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>359340</t>
+          <t>359361</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,85%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP16A07-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP16A07-Habitat-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -836,47 +836,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>28674</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>32818</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>28674</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>28674</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>28674</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>28674</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>32818</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>32818</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>32818</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>28674</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>28674</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>28674</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1179,47 +1179,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>41306</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>41647</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>41306</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>41306</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>41306</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>41306</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>41647</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>41647</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>41647</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>41306</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>41306</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>41306</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1522,47 +1522,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>35123</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>25164</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>35123</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>35123</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>35123</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>35123</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>25164</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>25164</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>25164</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>35123</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>35123</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>35123</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1865,47 +1865,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>38817</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>25677</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>38817</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>38817</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>38817</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>38817</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>25677</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>25677</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>25677</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>38817</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>38817</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>38817</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2208,47 +2208,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>125305</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>125305</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2783,47 +2783,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>34424</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>31446</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>34424</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>34424</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>34424</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>34424</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>31446</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>31446</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>31446</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>34424</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>34424</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>34424</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,107 +3013,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>656</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3909</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3324</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,6%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>9,53%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>8,1%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3246</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3277</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -3126,74 +3126,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>40320</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>40368</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>37115</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>37700</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>41024</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>98,4%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>90,47%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>91,9%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>40320</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>117</t>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>78067</t>
+          <t>78098</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>40320</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>40320</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>40320</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>41024</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>41024</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>41024</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>40320</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>40320</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>40320</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3469,47 +3469,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>35994</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>32964</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>35994</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>35994</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>35994</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>35994</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>32964</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>32964</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>32964</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>35994</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>35994</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>35994</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3812,47 +3812,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>47229</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>41786</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>47229</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>47229</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>47229</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>47229</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>41786</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>41786</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>41786</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>47229</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>47229</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>47229</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,107 +4042,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>656</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3768</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3255</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,45%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,56%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>2,21%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>3462</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>3038</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -4155,74 +4155,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>157966</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>146565</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>143453</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>143966</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>147221</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,55%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>97,44%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>97,79%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>157966</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>433</t>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>302149</t>
+          <t>301725</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>157966</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>157966</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>157966</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>212</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>147221</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>147221</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>147221</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>157966</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>157966</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>157966</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4730,47 +4730,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>24176</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>24359</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>24176</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>24176</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>24176</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>24176</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>24359</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>24359</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>24359</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>24176</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>24176</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>24176</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5073,47 +5073,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>41147</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>42699</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>41147</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>41147</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>41147</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>41147</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>42699</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>42699</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>42699</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>41147</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>41147</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>41147</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5416,47 +5416,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>27806</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>27615</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>27806</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>27806</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>27806</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>27806</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>27615</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>27615</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>27615</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>27806</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>27806</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>27806</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5759,47 +5759,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>30146</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>32788</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>30146</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>30146</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>30146</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>30146</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>32788</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>32788</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>32788</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>30146</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>30146</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>30146</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6102,47 +6102,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>192</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>127461</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>192</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>127461</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>127461</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>127461</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6677,64 +6677,64 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>24622</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>25841</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>26308</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>27660</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -6752,7 +6752,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>53501</t>
+          <t>50929</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>24622</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>24622</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>24622</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>25841</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>25841</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>25841</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>27660</t>
+          <t>26308</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>27660</t>
+          <t>26308</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27660</t>
+          <t>26308</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>53501</t>
+          <t>50929</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>53501</t>
+          <t>50929</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>53501</t>
+          <t>50929</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,107 +6907,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>713</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4035</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>653</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3291</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>1,81%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>9,12%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>9,11%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>653</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3646</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>713</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3662</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -7020,74 +7020,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>56458</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>43529</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>40207</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>44242</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>98,39%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>90,88%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>35483</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>32845</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>36136</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>98,19%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>90,89%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>63809</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>152</t>
@@ -7095,27 +7095,27 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>107338</t>
+          <t>91941</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>104389</t>
+          <t>88948</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>108051</t>
+          <t>92594</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>56458</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>56458</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>56458</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>44242</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>44242</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>44242</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>63809</t>
+          <t>36136</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>63809</t>
+          <t>36136</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>63809</t>
+          <t>36136</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>108051</t>
+          <t>92594</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>108051</t>
+          <t>92594</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>108051</t>
+          <t>92594</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,107 +7250,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1405</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5411</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1407</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4936</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>2,77%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7,02%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>9,71%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>1407</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>5072</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1405</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>4902</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -7363,74 +7363,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>52355</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>75666</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>71660</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>77071</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>98,18%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>92,98%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>49419</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>45890</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>50826</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>97,23%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>90,29%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>56923</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>145</t>
@@ -7438,27 +7438,27 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>132589</t>
+          <t>101774</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>129092</t>
+          <t>98109</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>133994</t>
+          <t>103181</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>52355</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>52355</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>52355</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>77071</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>77071</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>77071</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>56923</t>
+          <t>50826</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>56923</t>
+          <t>50826</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>56923</t>
+          <t>50826</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>133994</t>
+          <t>103181</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>133994</t>
+          <t>103181</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>133994</t>
+          <t>103181</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7706,64 +7706,64 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>31517</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>30561</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>29723</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>33809</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -7781,7 +7781,7 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>64370</t>
+          <t>61240</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>31517</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>31517</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>31517</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>30561</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>30561</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>30561</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>33809</t>
+          <t>29723</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>33809</t>
+          <t>29723</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>33809</t>
+          <t>29723</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>64370</t>
+          <t>61240</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>64370</t>
+          <t>61240</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>64370</t>
+          <t>61240</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>2118</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>497</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5750</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3,24%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2061</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>528</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6121</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>2118</t>
+          <t>2061</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>549</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5688</t>
+          <t>6470</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>175597</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>171965</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>177218</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>98,81%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>96,76%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,72%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>140931</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>136871</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>142464</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>357798</t>
+          <t>305883</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>354228</t>
+          <t>301474</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>359361</t>
+          <t>307395</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,82%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
